--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -776,37 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127359854</v>
+        <v>127354212</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>105478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -814,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560868</v>
+        <v>560846</v>
       </c>
       <c r="R3" t="n">
-        <v>6463629</v>
+        <v>6463681</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -850,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ca 50 st</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,38 +883,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127354212</v>
+        <v>127359854</v>
       </c>
       <c r="B4" t="n">
-        <v>105478</v>
+        <v>79632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -916,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560846</v>
+        <v>560868</v>
       </c>
       <c r="R4" t="n">
-        <v>6463681</v>
+        <v>6463629</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -952,11 +957,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ca 50 st</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -776,38 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127354212</v>
+        <v>127359854</v>
       </c>
       <c r="B3" t="n">
-        <v>105478</v>
+        <v>79632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560846</v>
+        <v>560868</v>
       </c>
       <c r="R3" t="n">
-        <v>6463681</v>
+        <v>6463629</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -851,11 +850,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ca 50 st</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,37 +877,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127359854</v>
+        <v>127354212</v>
       </c>
       <c r="B4" t="n">
-        <v>79632</v>
+        <v>105478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -921,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560868</v>
+        <v>560846</v>
       </c>
       <c r="R4" t="n">
-        <v>6463629</v>
+        <v>6463681</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -957,6 +952,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ca 50 st</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127354168</v>
       </c>
       <c r="B2" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,37 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127359854</v>
+        <v>127354212</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>105484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -814,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560868</v>
+        <v>560846</v>
       </c>
       <c r="R3" t="n">
-        <v>6463629</v>
+        <v>6463681</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -850,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ca 50 st</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,38 +883,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127354212</v>
+        <v>127359854</v>
       </c>
       <c r="B4" t="n">
-        <v>105478</v>
+        <v>79636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -916,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560846</v>
+        <v>560868</v>
       </c>
       <c r="R4" t="n">
-        <v>6463681</v>
+        <v>6463629</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -952,11 +957,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ca 50 st</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,7 +987,7 @@
         <v>127353847</v>
       </c>
       <c r="B5" t="n">
-        <v>57670</v>
+        <v>57674</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>127354120</v>
       </c>
       <c r="B6" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -776,38 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127354212</v>
+        <v>127359854</v>
       </c>
       <c r="B3" t="n">
-        <v>105484</v>
+        <v>79636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560846</v>
+        <v>560868</v>
       </c>
       <c r="R3" t="n">
-        <v>6463681</v>
+        <v>6463629</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -851,11 +850,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ca 50 st</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,37 +877,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127359854</v>
+        <v>127354212</v>
       </c>
       <c r="B4" t="n">
-        <v>79636</v>
+        <v>105484</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -921,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560868</v>
+        <v>560846</v>
       </c>
       <c r="R4" t="n">
-        <v>6463629</v>
+        <v>6463681</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -957,6 +952,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ca 50 st</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -776,37 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127359854</v>
+        <v>127354212</v>
       </c>
       <c r="B3" t="n">
-        <v>79636</v>
+        <v>105484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -814,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560868</v>
+        <v>560846</v>
       </c>
       <c r="R3" t="n">
-        <v>6463629</v>
+        <v>6463681</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -850,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ca 50 st</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,38 +883,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127354212</v>
+        <v>127359854</v>
       </c>
       <c r="B4" t="n">
-        <v>105484</v>
+        <v>79636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -916,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560846</v>
+        <v>560868</v>
       </c>
       <c r="R4" t="n">
-        <v>6463681</v>
+        <v>6463629</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -952,11 +957,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ca 50 st</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -776,38 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127354212</v>
+        <v>127359854</v>
       </c>
       <c r="B3" t="n">
-        <v>105484</v>
+        <v>79636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560846</v>
+        <v>560868</v>
       </c>
       <c r="R3" t="n">
-        <v>6463681</v>
+        <v>6463629</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -851,11 +850,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ca 50 st</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,37 +877,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127359854</v>
+        <v>127354212</v>
       </c>
       <c r="B4" t="n">
-        <v>79636</v>
+        <v>105486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -921,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560868</v>
+        <v>560846</v>
       </c>
       <c r="R4" t="n">
-        <v>6463629</v>
+        <v>6463681</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -957,6 +952,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ca 50 st</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127354168</v>
       </c>
       <c r="B2" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127359854</v>
       </c>
       <c r="B3" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127354212</v>
       </c>
       <c r="B4" t="n">
-        <v>105486</v>
+        <v>105488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>127353847</v>
       </c>
       <c r="B5" t="n">
-        <v>57674</v>
+        <v>57676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>127354120</v>
       </c>
       <c r="B6" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -880,7 +880,7 @@
         <v>127354212</v>
       </c>
       <c r="B4" t="n">
-        <v>105488</v>
+        <v>105494</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127354168</v>
       </c>
       <c r="B2" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127359854</v>
       </c>
       <c r="B3" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127354212</v>
       </c>
       <c r="B4" t="n">
-        <v>105494</v>
+        <v>105497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>127353847</v>
       </c>
       <c r="B5" t="n">
-        <v>57676</v>
+        <v>57679</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>127354120</v>
       </c>
       <c r="B6" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127354168</v>
       </c>
       <c r="B2" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127359854</v>
       </c>
       <c r="B3" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127354212</v>
       </c>
       <c r="B4" t="n">
-        <v>105497</v>
+        <v>105505</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>127353847</v>
       </c>
       <c r="B5" t="n">
-        <v>57679</v>
+        <v>57685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>127354120</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -776,37 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127359854</v>
+        <v>127354212</v>
       </c>
       <c r="B3" t="n">
-        <v>79647</v>
+        <v>105506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -814,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560868</v>
+        <v>560846</v>
       </c>
       <c r="R3" t="n">
-        <v>6463629</v>
+        <v>6463681</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -850,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ca 50 st</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,38 +883,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127354212</v>
+        <v>127359854</v>
       </c>
       <c r="B4" t="n">
-        <v>105505</v>
+        <v>79647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -916,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560846</v>
+        <v>560868</v>
       </c>
       <c r="R4" t="n">
-        <v>6463681</v>
+        <v>6463629</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -952,11 +957,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ca 50 st</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -776,38 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127354212</v>
+        <v>127359854</v>
       </c>
       <c r="B3" t="n">
-        <v>105506</v>
+        <v>79647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560846</v>
+        <v>560868</v>
       </c>
       <c r="R3" t="n">
-        <v>6463681</v>
+        <v>6463629</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -851,11 +850,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ca 50 st</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,37 +877,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127359854</v>
+        <v>127354212</v>
       </c>
       <c r="B4" t="n">
-        <v>79647</v>
+        <v>105506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -921,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560868</v>
+        <v>560846</v>
       </c>
       <c r="R4" t="n">
-        <v>6463629</v>
+        <v>6463681</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -957,6 +952,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ca 50 st</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -880,7 +880,7 @@
         <v>127354212</v>
       </c>
       <c r="B4" t="n">
-        <v>105506</v>
+        <v>105507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -880,7 +880,7 @@
         <v>127354212</v>
       </c>
       <c r="B4" t="n">
-        <v>105507</v>
+        <v>105508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1221,6 +1221,335 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128726936</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91486</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Risten-Mulstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>560876</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6463616</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128726891</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57686</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Risten-Mulstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>560850</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6463661</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Den drumade intensivt och även ropade då och då under mitt ca 2,5 timmar långa besök, vilket är lite ovanligt nu på hösten och nog är ett tydlig tecken på att den ca 160 till 170 åriga kontinuitetsskogen är en mycket viktig del av dess revir. Mycket riktig finns det också boträdet med bohålet som används för övernattning i den gamla skogen och även mycket hackspår efter födosök.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128726626</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98588</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Risten-Mulstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>560839</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6463694</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -1449,7 +1449,7 @@
         <v>128726626</v>
       </c>
       <c r="B9" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>128726936</v>
       </c>
       <c r="B7" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,54 +1324,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128726891</v>
+        <v>128726626</v>
       </c>
       <c r="B8" t="n">
-        <v>57686</v>
+        <v>98592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1379,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560850</v>
+        <v>560839</v>
       </c>
       <c r="R8" t="n">
-        <v>6463661</v>
+        <v>6463694</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,17 +1405,13 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Den drumade intensivt och även ropade då och då under mitt ca 2,5 timmar långa besök, vilket är lite ovanligt nu på hösten och nog är ett tydlig tecken på att den ca 160 till 170 åriga kontinuitetsskogen är en mycket viktig del av dess revir. Mycket riktig finns det också boträdet med bohålet som används för övernattning i den gamla skogen och även mycket hackspår efter födosök.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1446,42 +1430,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128726626</v>
+        <v>128726891</v>
       </c>
       <c r="B9" t="n">
-        <v>98591</v>
+        <v>57686</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1489,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560839</v>
+        <v>560850</v>
       </c>
       <c r="R9" t="n">
-        <v>6463694</v>
+        <v>6463661</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,13 +1523,17 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Den drumade intensivt och även ropade då och då under mitt ca 2,5 timmar långa besök, vilket är lite ovanligt nu på hösten och nog är ett tydlig tecken på att den ca 160 till 170 åriga kontinuitetsskogen är en mycket viktig del av dess revir. Mycket riktig finns det också boträdet med bohålet som används för övernattning i den gamla skogen och även mycket hackspår efter födosök.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>128726936</v>
       </c>
       <c r="B7" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,42 +1324,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128726626</v>
+        <v>128726891</v>
       </c>
       <c r="B8" t="n">
-        <v>98592</v>
+        <v>57713</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1367,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560839</v>
+        <v>560850</v>
       </c>
       <c r="R8" t="n">
-        <v>6463694</v>
+        <v>6463661</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,13 +1417,17 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Den drumade intensivt och även ropade då och då under mitt ca 2,5 timmar långa besök, vilket är lite ovanligt nu på hösten och nog är ett tydlig tecken på att den ca 160 till 170 åriga kontinuitetsskogen är en mycket viktig del av dess revir. Mycket riktig finns det också boträdet med bohålet som används för övernattning i den gamla skogen och även mycket hackspår efter födosök.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1430,54 +1446,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128726891</v>
+        <v>128726626</v>
       </c>
       <c r="B9" t="n">
-        <v>57686</v>
+        <v>98619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1485,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560850</v>
+        <v>560839</v>
       </c>
       <c r="R9" t="n">
-        <v>6463661</v>
+        <v>6463694</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,17 +1527,13 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Den drumade intensivt och även ropade då och då under mitt ca 2,5 timmar långa besök, vilket är lite ovanligt nu på hösten och nog är ett tydlig tecken på att den ca 160 till 170 åriga kontinuitetsskogen är en mycket viktig del av dess revir. Mycket riktig finns det också boträdet med bohålet som används för övernattning i den gamla skogen och även mycket hackspår efter födosök.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>128726936</v>
       </c>
       <c r="B7" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128726626</v>
       </c>
       <c r="B9" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>128726936</v>
       </c>
       <c r="B7" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,54 +1324,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128726891</v>
+        <v>128726626</v>
       </c>
       <c r="B8" t="n">
-        <v>57713</v>
+        <v>98632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1379,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560850</v>
+        <v>560839</v>
       </c>
       <c r="R8" t="n">
-        <v>6463661</v>
+        <v>6463694</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,17 +1405,13 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Den drumade intensivt och även ropade då och då under mitt ca 2,5 timmar långa besök, vilket är lite ovanligt nu på hösten och nog är ett tydlig tecken på att den ca 160 till 170 åriga kontinuitetsskogen är en mycket viktig del av dess revir. Mycket riktig finns det också boträdet med bohålet som används för övernattning i den gamla skogen och även mycket hackspår efter födosök.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1446,42 +1430,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128726626</v>
+        <v>128726891</v>
       </c>
       <c r="B9" t="n">
-        <v>98625</v>
+        <v>57713</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1489,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560839</v>
+        <v>560850</v>
       </c>
       <c r="R9" t="n">
-        <v>6463694</v>
+        <v>6463661</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,13 +1523,17 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Den drumade intensivt och även ropade då och då under mitt ca 2,5 timmar långa besök, vilket är lite ovanligt nu på hösten och nog är ett tydlig tecken på att den ca 160 till 170 åriga kontinuitetsskogen är en mycket viktig del av dess revir. Mycket riktig finns det också boträdet med bohålet som används för övernattning i den gamla skogen och även mycket hackspår efter födosök.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>128726936</v>
       </c>
       <c r="B7" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,42 +1324,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128726626</v>
+        <v>128726891</v>
       </c>
       <c r="B8" t="n">
-        <v>98632</v>
+        <v>57717</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1367,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560839</v>
+        <v>560850</v>
       </c>
       <c r="R8" t="n">
-        <v>6463694</v>
+        <v>6463661</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,13 +1417,17 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Den drumade intensivt och även ropade då och då under mitt ca 2,5 timmar långa besök, vilket är lite ovanligt nu på hösten och nog är ett tydlig tecken på att den ca 160 till 170 åriga kontinuitetsskogen är en mycket viktig del av dess revir. Mycket riktig finns det också boträdet med bohålet som används för övernattning i den gamla skogen och även mycket hackspår efter födosök.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1430,54 +1446,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128726891</v>
+        <v>128726626</v>
       </c>
       <c r="B9" t="n">
-        <v>57713</v>
+        <v>98636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1485,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560850</v>
+        <v>560839</v>
       </c>
       <c r="R9" t="n">
-        <v>6463661</v>
+        <v>6463694</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,17 +1527,13 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Den drumade intensivt och även ropade då och då under mitt ca 2,5 timmar långa besök, vilket är lite ovanligt nu på hösten och nog är ett tydlig tecken på att den ca 160 till 170 åriga kontinuitetsskogen är en mycket viktig del av dess revir. Mycket riktig finns det också boträdet med bohålet som används för övernattning i den gamla skogen och även mycket hackspår efter födosök.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -1324,54 +1324,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128726891</v>
+        <v>128726626</v>
       </c>
       <c r="B8" t="n">
-        <v>57717</v>
+        <v>98636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1379,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560850</v>
+        <v>560839</v>
       </c>
       <c r="R8" t="n">
-        <v>6463661</v>
+        <v>6463694</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,17 +1405,13 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Den drumade intensivt och även ropade då och då under mitt ca 2,5 timmar långa besök, vilket är lite ovanligt nu på hösten och nog är ett tydlig tecken på att den ca 160 till 170 åriga kontinuitetsskogen är en mycket viktig del av dess revir. Mycket riktig finns det också boträdet med bohålet som används för övernattning i den gamla skogen och även mycket hackspår efter födosök.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1446,42 +1430,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128726626</v>
+        <v>128726891</v>
       </c>
       <c r="B9" t="n">
-        <v>98636</v>
+        <v>57717</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1489,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560839</v>
+        <v>560850</v>
       </c>
       <c r="R9" t="n">
-        <v>6463694</v>
+        <v>6463661</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,13 +1523,17 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Den drumade intensivt och även ropade då och då under mitt ca 2,5 timmar långa besök, vilket är lite ovanligt nu på hösten och nog är ett tydlig tecken på att den ca 160 till 170 åriga kontinuitetsskogen är en mycket viktig del av dess revir. Mycket riktig finns det också boträdet med bohålet som används för övernattning i den gamla skogen och även mycket hackspår efter födosök.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>128726936</v>
       </c>
       <c r="B7" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>128726626</v>
       </c>
       <c r="B8" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>128726891</v>
       </c>
       <c r="B9" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>128726936</v>
       </c>
       <c r="B7" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128726626</v>
       </c>
       <c r="B9" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>128726936</v>
       </c>
       <c r="B7" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,54 +1324,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128726891</v>
+        <v>128726626</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1379,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560850</v>
+        <v>560839</v>
       </c>
       <c r="R8" t="n">
-        <v>6463661</v>
+        <v>6463694</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,17 +1405,13 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Den drumade intensivt och även ropade då och då under mitt ca 2,5 timmar långa besök, vilket är lite ovanligt nu på hösten och nog är ett tydlig tecken på att den ca 160 till 170 åriga kontinuitetsskogen är en mycket viktig del av dess revir. Mycket riktig finns det också boträdet med bohålet som används för övernattning i den gamla skogen och även mycket hackspår efter födosök.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1446,42 +1430,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128726626</v>
+        <v>128726891</v>
       </c>
       <c r="B9" t="n">
-        <v>98656</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1489,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560839</v>
+        <v>560850</v>
       </c>
       <c r="R9" t="n">
-        <v>6463694</v>
+        <v>6463661</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,13 +1523,17 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Den drumade intensivt och även ropade då och då under mitt ca 2,5 timmar långa besök, vilket är lite ovanligt nu på hösten och nog är ett tydlig tecken på att den ca 160 till 170 åriga kontinuitetsskogen är en mycket viktig del av dess revir. Mycket riktig finns det också boträdet med bohålet som används för övernattning i den gamla skogen och även mycket hackspår efter födosök.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -1324,42 +1324,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128726626</v>
+        <v>128726891</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>57720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1367,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560839</v>
+        <v>560850</v>
       </c>
       <c r="R8" t="n">
-        <v>6463694</v>
+        <v>6463661</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,13 +1417,17 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Den drumade intensivt och även ropade då och då under mitt ca 2,5 timmar långa besök, vilket är lite ovanligt nu på hösten och nog är ett tydlig tecken på att den ca 160 till 170 åriga kontinuitetsskogen är en mycket viktig del av dess revir. Mycket riktig finns det också boträdet med bohålet som används för övernattning i den gamla skogen och även mycket hackspår efter födosök.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1430,54 +1446,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128726891</v>
+        <v>128726626</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>98659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1485,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560850</v>
+        <v>560839</v>
       </c>
       <c r="R9" t="n">
-        <v>6463661</v>
+        <v>6463694</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,17 +1527,13 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Den drumade intensivt och även ropade då och då under mitt ca 2,5 timmar långa besök, vilket är lite ovanligt nu på hösten och nog är ett tydlig tecken på att den ca 160 till 170 åriga kontinuitetsskogen är en mycket viktig del av dess revir. Mycket riktig finns det också boträdet med bohålet som används för övernattning i den gamla skogen och även mycket hackspår efter födosök.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -1324,54 +1324,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128726891</v>
+        <v>128726626</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1379,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560850</v>
+        <v>560839</v>
       </c>
       <c r="R8" t="n">
-        <v>6463661</v>
+        <v>6463694</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,17 +1405,13 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Den drumade intensivt och även ropade då och då under mitt ca 2,5 timmar långa besök, vilket är lite ovanligt nu på hösten och nog är ett tydlig tecken på att den ca 160 till 170 åriga kontinuitetsskogen är en mycket viktig del av dess revir. Mycket riktig finns det också boträdet med bohålet som används för övernattning i den gamla skogen och även mycket hackspår efter födosök.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1446,42 +1430,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128726626</v>
+        <v>128726891</v>
       </c>
       <c r="B9" t="n">
-        <v>98659</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1489,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560839</v>
+        <v>560850</v>
       </c>
       <c r="R9" t="n">
-        <v>6463694</v>
+        <v>6463661</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,13 +1523,17 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Den drumade intensivt och även ropade då och då under mitt ca 2,5 timmar långa besök, vilket är lite ovanligt nu på hösten och nog är ett tydlig tecken på att den ca 160 till 170 åriga kontinuitetsskogen är en mycket viktig del av dess revir. Mycket riktig finns det också boträdet med bohålet som används för övernattning i den gamla skogen och även mycket hackspår efter födosök.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>128726936</v>
       </c>
       <c r="B7" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,42 +1324,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128726626</v>
+        <v>128726891</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>57722</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1367,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560839</v>
+        <v>560850</v>
       </c>
       <c r="R8" t="n">
-        <v>6463694</v>
+        <v>6463661</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,13 +1417,17 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Den drumade intensivt och även ropade då och då under mitt ca 2,5 timmar långa besök, vilket är lite ovanligt nu på hösten och nog är ett tydlig tecken på att den ca 160 till 170 åriga kontinuitetsskogen är en mycket viktig del av dess revir. Mycket riktig finns det också boträdet med bohålet som används för övernattning i den gamla skogen och även mycket hackspår efter födosök.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1430,54 +1446,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128726891</v>
+        <v>128726626</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>98669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1485,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560850</v>
+        <v>560839</v>
       </c>
       <c r="R9" t="n">
-        <v>6463661</v>
+        <v>6463694</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,17 +1527,13 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Den drumade intensivt och även ropade då och då under mitt ca 2,5 timmar långa besök, vilket är lite ovanligt nu på hösten och nog är ett tydlig tecken på att den ca 160 till 170 åriga kontinuitetsskogen är en mycket viktig del av dess revir. Mycket riktig finns det också boträdet med bohålet som används för övernattning i den gamla skogen och även mycket hackspår efter födosök.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>128726936</v>
       </c>
       <c r="B7" t="n">
-        <v>91553</v>
+        <v>91562</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>128726891</v>
       </c>
       <c r="B8" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128726626</v>
       </c>
       <c r="B9" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1550,6 +1550,116 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129874744</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Risten-Mulstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>560813</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6463691</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>E-Åtv-0286</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -1555,7 +1555,7 @@
         <v>129874744</v>
       </c>
       <c r="B10" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -1555,7 +1555,7 @@
         <v>129874744</v>
       </c>
       <c r="B10" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -1555,7 +1555,7 @@
         <v>129874744</v>
       </c>
       <c r="B10" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -1555,7 +1555,7 @@
         <v>129874744</v>
       </c>
       <c r="B10" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -1555,7 +1555,7 @@
         <v>129874744</v>
       </c>
       <c r="B10" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -1555,7 +1555,7 @@
         <v>129874744</v>
       </c>
       <c r="B10" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -1555,7 +1555,7 @@
         <v>129874744</v>
       </c>
       <c r="B10" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -1555,7 +1555,7 @@
         <v>129874744</v>
       </c>
       <c r="B10" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -987,7 +987,7 @@
         <v>127353847</v>
       </c>
       <c r="B5" t="n">
-        <v>57897</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>127354120</v>
       </c>
       <c r="B6" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>128726891</v>
       </c>
       <c r="B8" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -987,7 +987,7 @@
         <v>127353847</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>57900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>127354120</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>128726891</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -987,7 +987,7 @@
         <v>127353847</v>
       </c>
       <c r="B5" t="n">
-        <v>57900</v>
+        <v>57901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>127354120</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>128726891</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -987,7 +987,7 @@
         <v>127353847</v>
       </c>
       <c r="B5" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>127354120</v>
       </c>
       <c r="B6" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>128726891</v>
       </c>
       <c r="B8" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -987,7 +987,7 @@
         <v>127353847</v>
       </c>
       <c r="B5" t="n">
-        <v>57904</v>
+        <v>57905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>127354120</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>128726891</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -987,7 +987,7 @@
         <v>127353847</v>
       </c>
       <c r="B5" t="n">
-        <v>57905</v>
+        <v>57911</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>127354120</v>
       </c>
       <c r="B6" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>128726891</v>
       </c>
       <c r="B8" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -987,7 +987,7 @@
         <v>127353847</v>
       </c>
       <c r="B5" t="n">
-        <v>57911</v>
+        <v>57912</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>127354120</v>
       </c>
       <c r="B6" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>128726891</v>
       </c>
       <c r="B8" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -987,7 +987,7 @@
         <v>127353847</v>
       </c>
       <c r="B5" t="n">
-        <v>57912</v>
+        <v>57915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>127354120</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>128726891</v>
       </c>
       <c r="B8" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 1845-2022 artfynd.xlsx
+++ b/artfynd/A 1845-2022 artfynd.xlsx
@@ -987,7 +987,7 @@
         <v>127353847</v>
       </c>
       <c r="B5" t="n">
-        <v>57915</v>
+        <v>57917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>127354120</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>128726891</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
